--- a/xubi_backend/src/main/resources/网站数据.xlsx
+++ b/xubi_backend/src/main/resources/网站数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CodeRoad\xu_bi\xubi_backend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C996DC-BA5E-45D6-A06D-2BE5C3875633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D285DF-F9BB-4B07-A626-338274D05267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{229EEA6E-F8A7-2545-904A-8F0032855BE1}"/>
   </bookViews>
@@ -525,16 +525,16 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
-        <v>50</v>
+      <c r="B6" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
-        <v>60</v>
+      <c r="B7" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.6">
@@ -542,15 +542,15 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3">
-        <v>80</v>
+      <c r="B9" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.6">
